--- a/public/Refs/minifinance_doc.xlsx
+++ b/public/Refs/minifinance_doc.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lthnot0\Documents\00_JOB\71_Minifinancial\minifinancial\public\Refs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\00-Jobs\MyDevs\90_MiniFinancial\minifinancial\public\Refs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE88F315-475A-4C6E-AA49-4F69C449410C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CB9781-CA54-496A-86B7-9F37AE7596FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{53700104-613C-48F6-9933-DEA61E9F00CA}"/>
+    <workbookView xWindow="-28920" yWindow="-2685" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{53700104-613C-48F6-9933-DEA61E9F00CA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="5" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet2!$A$3:$E$31</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -28,8 +33,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="207">
   <si>
     <t>Or in a normalized mapping table:</t>
   </si>
@@ -307,13 +310,367 @@
   </si>
   <si>
     <t xml:space="preserve">Debit </t>
+  </si>
+  <si>
+    <t>Deposit(ฝากเงิน)</t>
+  </si>
+  <si>
+    <t>Cash &amp; Deposits(เงินสดและเงินฝาก)</t>
+  </si>
+  <si>
+    <t>Cash / SavingsAccount / FixedDeposit(เงินสด / บัญชีออมทรัพย์ / บัญชีฝากประจำ)</t>
+  </si>
+  <si>
+    <t>Cash / SavingsAccount(เงินสด / บัญชีออมทรัพย์)</t>
+  </si>
+  <si>
+    <t>Withdrawal(ถอนเงิน)</t>
+  </si>
+  <si>
+    <t>Cash(เงินสด)</t>
+  </si>
+  <si>
+    <t>SavingsAccount / FixedDeposit(บัญชีออมทรัพย์ / บัญชีฝากประจำ)</t>
+  </si>
+  <si>
+    <t>Transfer(โอนเงิน)</t>
+  </si>
+  <si>
+    <t>Destination Account(บัญชีปลายทาง)</t>
+  </si>
+  <si>
+    <t>Source Account(บัญชีต้นทาง)</t>
+  </si>
+  <si>
+    <t>Interest Income(รายได้ดอกเบี้ย)</t>
+  </si>
+  <si>
+    <t>Income(รายได้)</t>
+  </si>
+  <si>
+    <t>Loan Issued(การปล่อยกู้)</t>
+  </si>
+  <si>
+    <t>Loans Receivable(ลูกหนี้เงินให้กู้ยืม)</t>
+  </si>
+  <si>
+    <t>PersonalLoan / BusinessLoan(สินเชื่อส่วนบุคคล / สินเชื่อธุรกิจ)</t>
+  </si>
+  <si>
+    <t>Loan Repayment(การชำระคืนเงินกู้)</t>
+  </si>
+  <si>
+    <t>Interest Accrual(ดอกเบี้ยค้างรับ)</t>
+  </si>
+  <si>
+    <t>Bad Debt Write-Off(ตัดจำหน่ายหนี้สูญ)</t>
+  </si>
+  <si>
+    <t>Expense(ค่าใช้จ่าย)</t>
+  </si>
+  <si>
+    <t>Bad Debt Expense(ค่าใช้จ่ายหนี้สูญ)</t>
+  </si>
+  <si>
+    <t>ReFinance(รีไฟแนนซ์)</t>
+  </si>
+  <si>
+    <t>New Loan(เงินกู้ใหม่)</t>
+  </si>
+  <si>
+    <t>Existing Loan(เงินกู้เดิม)</t>
+  </si>
+  <si>
+    <t>Broker Payment(ชำระค่าธรรมเนียมโบรกเกอร์)</t>
+  </si>
+  <si>
+    <t>Brokerage Fee(ค่าธรรมเนียมโบรกเกอร์)</t>
+  </si>
+  <si>
+    <t>Security Purchase(ซื้อตราสารหนี้)</t>
+  </si>
+  <si>
+    <t>Securities(ตราสารหนี้)</t>
+  </si>
+  <si>
+    <t>GovernmentBond / CorporateBond(พันธบัตรรัฐบาล / หุ้นกู้เอกชน)</t>
+  </si>
+  <si>
+    <t>Security Sale(ขายตราสารหนี้)</t>
+  </si>
+  <si>
+    <t>Coupon Payment(รับดอกเบี้ยหุ้นกู้/คูปอง)</t>
+  </si>
+  <si>
+    <t>Fair Value Adjustment (Gain)(ปรับมูลค่ายุติธรรม - กำไร)</t>
+  </si>
+  <si>
+    <t>Unrealized Gain(กำไรที่ยังไม่เกิดขึ้นจริง)</t>
+  </si>
+  <si>
+    <t>Fair Value Adjustment (Loss)(ปรับมูลค่ายุติธรรม - ขาดทุน)</t>
+  </si>
+  <si>
+    <t>Unrealized Loss(ขาดทุนที่ยังไม่เกิดขึ้นจริง)</t>
+  </si>
+  <si>
+    <t>Equity Purchase(ซื้อหุ้นทุน)</t>
+  </si>
+  <si>
+    <t>Equity Holdings(เงินลงทุนในตราสารทุน)</t>
+  </si>
+  <si>
+    <t>ListedEquity / PrivateEquity(หุ้นจดทะเบียน / หุ้นนอกตลาด)</t>
+  </si>
+  <si>
+    <t>Equity Sale(ขายหุ้นทุน)</t>
+  </si>
+  <si>
+    <t>Dividend Received(รับเงินปันผล)</t>
+  </si>
+  <si>
+    <t>Dividend Income(รายได้เงินปันผล)</t>
+  </si>
+  <si>
+    <t>Equity Method Adjustment(ปรับปรุงตามวิธีส่วนได้เสีย)</t>
+  </si>
+  <si>
+    <t>Equity Method Gain(กำไรตามวิธีส่วนได้เสีย)</t>
+  </si>
+  <si>
+    <t>Real Estate Purchase(ซื้ออสังหาริมทรัพย์)</t>
+  </si>
+  <si>
+    <t>Other Investments(เงินลงทุนอื่น)</t>
+  </si>
+  <si>
+    <t>RealEstate(อสังหาริมทรัพย์)</t>
+  </si>
+  <si>
+    <t>Rental Income(รายได้ค่าเช่า)</t>
+  </si>
+  <si>
+    <t>Mutual Fund Investment(ลงทุนในกองทุนรวม)</t>
+  </si>
+  <si>
+    <t>MutualFund(กองทุนรวม)</t>
+  </si>
+  <si>
+    <t>Disposal Gain(กำไรจากการจำหน่ายทรัพย์สิน)</t>
+  </si>
+  <si>
+    <t>RealEstate / MutualFund(อสังหาริมทรัพย์ / กองทุนรวม)</t>
+  </si>
+  <si>
+    <t>Disposal Loss(ขาดทุนจากการจำหน่ายทรัพย์สิน)</t>
+  </si>
+  <si>
+    <t>Saving Share Payment(ชำระค่าหุ้นออมทรัพย์)</t>
+  </si>
+  <si>
+    <t>CommunitySavingShare(หุ้นออมทรัพย์ชุมชน)</t>
+  </si>
+  <si>
+    <t>Saving Share Income(รายได้หุ้นออมทรัพย์)</t>
+  </si>
+  <si>
+    <t>Insurance Premium(ชำระเบี้ยประกันภัย)</t>
+  </si>
+  <si>
+    <t>Insurance(ประกันภัย)</t>
+  </si>
+  <si>
+    <t>Insurance Benefit(รับผลประโยชน์ประกันภัย)</t>
+  </si>
+  <si>
+    <t>Session / Transaction Type</t>
+  </si>
+  <si>
+    <t>Cash / SavingsAccount / FixedDeposit(เงินสด / ออมทรัพย์ / ฝากประจำ)</t>
+  </si>
+  <si>
+    <t>Drawdown(เบิก/รับเงินกู้ยืม)</t>
+  </si>
+  <si>
+    <t>Borrowings(เงินกู้ยืม)</t>
+  </si>
+  <si>
+    <t>ShortTermLoan / LongTermLoan / Mortgage(เงินกู้ระยะสั้น / ระยะยาว / จำนอง)</t>
+  </si>
+  <si>
+    <t>Repayment(ชำระคืนเงินกู้)</t>
+  </si>
+  <si>
+    <t>Borrowing Interest Accrual(ตั้งดอกเบี้ยค้างจ่าย)</t>
+  </si>
+  <si>
+    <t>InterestExpense(ดอกเบี้ยจ่าย)</t>
+  </si>
+  <si>
+    <t>BorrowingInterest(ดอกเบี้ยเงินกู้ยืม)</t>
+  </si>
+  <si>
+    <t>Payables(เจ้าหนี้การค้า/อื่น ๆ)</t>
+  </si>
+  <si>
+    <t>AccruedExpense(ค่าใช้จ่ายค้างจ่าย)</t>
+  </si>
+  <si>
+    <t>Borrowing Refinance(รีไฟแนนซ์หนี้)</t>
+  </si>
+  <si>
+    <t>ShortTermLoan(เงินกู้ใหม่)</t>
+  </si>
+  <si>
+    <t>LongTermLoan(เงินกู้เดิม)</t>
+  </si>
+  <si>
+    <t>Invoice Received(รับใบแจ้งหนี้/ตั้งเจ้าหนี้)</t>
+  </si>
+  <si>
+    <t>OperatingExpense(ค่าใช้จ่ายดำเนินงาน)</t>
+  </si>
+  <si>
+    <t>Administrative / BrokerageFee(ค่าบริหารทั่วไป / ค่าธรรมเนียม)</t>
+  </si>
+  <si>
+    <t>AccountsPayable(เจ้าหนี้การค้า)</t>
+  </si>
+  <si>
+    <t>Payment Made(ชำระเงินให้เจ้าหนี้)</t>
+  </si>
+  <si>
+    <t>AccountsPayable / AccruedExpense(เจ้าหนี้การค้า / ค่าใช้จ่ายค้างจ่าย)</t>
+  </si>
+  <si>
+    <t>Credit Note Received(รับใบลดหนี้)</t>
+  </si>
+  <si>
+    <t>Administrative(ค่าใช้จ่ายบริหารทั่วไป)</t>
+  </si>
+  <si>
+    <t>Service Invoiced(ออกใบแจ้งหนี้/รับรู้รายได้)</t>
+  </si>
+  <si>
+    <t>LoansReceivable / Cash &amp; Deposits(ลูกหนี้ / เงินสด)</t>
+  </si>
+  <si>
+    <t>BusinessLoan / Cash(สินเชื่อธุรกิจ / เงินสด)</t>
+  </si>
+  <si>
+    <t>OperatingRevenue(รายได้การดำเนินงาน)</t>
+  </si>
+  <si>
+    <t>SalesRevenue / ServiceRevenue(รายได้ขาย / รายได้บริการ)</t>
+  </si>
+  <si>
+    <t>Operating Revenue Recognition(รับรู้รายได้ค่าเช่า/บริการ)</t>
+  </si>
+  <si>
+    <t>RentalIncome / ServiceRevenue(รายได้ค่าเช่า / บริการ)</t>
+  </si>
+  <si>
+    <t>Interest Received(รับดอกเบี้ย)</t>
+  </si>
+  <si>
+    <t>InterestIncome(รายได้ดอกเบี้ย)</t>
+  </si>
+  <si>
+    <t>BankInterest / LoanInterest / BondCoupon(ดอกเบี้ยธนาคาร / ดอกเบี้ยกู้ / คูปอง)</t>
+  </si>
+  <si>
+    <t>Interest Accrued (Receivable)(รับรู้ดอกเบี้ยค้างรับ)</t>
+  </si>
+  <si>
+    <t>LoansReceivable(ลูกหนี้เงินให้กู้ยืม)</t>
+  </si>
+  <si>
+    <t>PersonalLoan / BusinessLoan(สินเชื่อส่วนบุคคล / ธุรกิจ)</t>
+  </si>
+  <si>
+    <t>LoanInterest(ดอกเบี้ยรับจากการปล่อยกู้)</t>
+  </si>
+  <si>
+    <t>Dividend Received (Revenue)(รับเงินปันผล)</t>
+  </si>
+  <si>
+    <t>DividendIncome(รายได้เงินปันผล)</t>
+  </si>
+  <si>
+    <t>ListedDividend / PrivateDividend / FundDividend(ปันผลหุ้นในตลาด / นอกตลาด / กองทุน)</t>
+  </si>
+  <si>
+    <t>Expense Incurred(ตั้งค่าใช้จ่าย)</t>
+  </si>
+  <si>
+    <t>Administrative / InsurancePremium(ค่าบริหารทั่วไป / เบี้ยประกันภัย)</t>
+  </si>
+  <si>
+    <t>Expense Paid(จ่ายค่าใช้จ่าย)</t>
+  </si>
+  <si>
+    <t>Broker Fee Paid(จ่ายค่าธรรมเนียมโบรกเกอร์)</t>
+  </si>
+  <si>
+    <t>BrokerageFee(ค่าธรรมเนียมโบรกเกอร์)</t>
+  </si>
+  <si>
+    <t>Interest Expense Accrued(ตั้งดอกเบี้ยจ่ายค้างชำระ)</t>
+  </si>
+  <si>
+    <t>BankLoanInterest / BorrowingInterest(ดอกเบี้ยธนาคาร / ดอกเบี้ยเงินกู้)</t>
+  </si>
+  <si>
+    <t>Interest Paid(จ่ายดอกเบี้ย)</t>
+  </si>
+  <si>
+    <t>Bad Debt Provision Recognized(รับรู้ค่าเผื่อหนี้สงสัยจะสูญ)</t>
+  </si>
+  <si>
+    <t>BadDebtExpense(ค่าเผื่อหนี้สงสัยจะสูญ)</t>
+  </si>
+  <si>
+    <t>AllowanceForBadDebt(ค่าเผื่อหนี้สงสัยจะสูญ)</t>
+  </si>
+  <si>
+    <t>Bad Debt Written Off(ตัดจำหน่ายหนี้สูญ)</t>
+  </si>
+  <si>
+    <t>BadDebtExpense(ค่าใช้จ่ายหนี้สูญ)</t>
+  </si>
+  <si>
+    <t>BadDebtWriteOff(ตัดจำหน่ายหนี้สูญ)</t>
+  </si>
+  <si>
+    <t>Asset Disposed (Loss)(จำหน่ายทรัพย์สินขาดทุน)</t>
+  </si>
+  <si>
+    <t>DisposalLoss(ขาดทุนจากการจำหน่าย)</t>
+  </si>
+  <si>
+    <t>DisposalLoss(ขาดทุนจากการจำหน่ายทรัพย์สิน)</t>
+  </si>
+  <si>
+    <t>OtherInvestments(เงินลงทุนอื่น)</t>
+  </si>
+  <si>
+    <t>Fair Value Loss Adjusted(ปรับมูลค่ายุติธรรม - ขาดทุน)</t>
+  </si>
+  <si>
+    <t>UnrealizedLoss(ขาดทุนที่ยังไม่เกิดขึ้นจริง)</t>
+  </si>
+  <si>
+    <t>Securities / EquityHoldings(ตราสารหนี้ / ตราสารทุน)</t>
+  </si>
+  <si>
+    <t>GovernmentBond / ListedEquity(พันธบัตร / หุ้นจดทะเบียน)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -334,8 +691,14 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -348,8 +711,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -424,11 +793,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -453,6 +837,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -789,22 +1179,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EBD9357-A7A9-4BD3-ACEF-1AD2A4BDB738}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
+    <col min="1" max="1" width="23.875" customWidth="1"/>
+    <col min="2" max="2" width="26.25" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="16.5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="17.25" thickBot="1">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:3" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="17.25" thickBot="1">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -815,7 +1205,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="17.25" thickBot="1">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -826,7 +1216,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="33.75" thickBot="1">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
@@ -837,7 +1227,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="33.75" thickBot="1">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
@@ -848,7 +1238,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="231.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="66.75" thickBot="1">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -859,7 +1249,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="231.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="66.75" thickBot="1">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -870,7 +1260,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="182.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="66.75" thickBot="1">
       <c r="A9" s="4" t="s">
         <v>14</v>
       </c>
@@ -881,7 +1271,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="182.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="66.75" thickBot="1">
       <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
@@ -892,7 +1282,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="182.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="50.25" thickBot="1">
       <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
@@ -903,7 +1293,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="182.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="50.25" thickBot="1">
       <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
@@ -914,7 +1304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="149.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="50.25" thickBot="1">
       <c r="A13" s="4" t="s">
         <v>22</v>
       </c>
@@ -925,7 +1315,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="116.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="33.75" thickBot="1">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
@@ -936,7 +1326,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="99.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="33.75" thickBot="1">
       <c r="A15" s="4" t="s">
         <v>22</v>
       </c>
@@ -947,7 +1337,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="33.75" thickBot="1">
       <c r="A16" s="4" t="s">
         <v>22</v>
       </c>
@@ -966,16 +1356,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A57E0C-DCCD-4800-B698-F1F14306031D}">
   <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="1" max="1" width="20.25" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" customWidth="1"/>
+    <col min="3" max="3" width="23.625" customWidth="1"/>
+    <col min="4" max="4" width="19.625" customWidth="1"/>
     <col min="5" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1">
       <c r="A1" s="5" t="s">
         <v>32</v>
       </c>
@@ -990,7 +1380,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="17.25" thickBot="1">
       <c r="A2" s="6"/>
       <c r="B2" s="3" t="s">
         <v>33</v>
@@ -1005,7 +1395,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="33.75" thickBot="1">
       <c r="A3" s="4" t="s">
         <v>37</v>
       </c>
@@ -1022,7 +1412,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="17.25" thickBot="1">
       <c r="A4" s="4" t="s">
         <v>41</v>
       </c>
@@ -1039,7 +1429,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="17.25" thickBot="1">
       <c r="A5" s="4" t="s">
         <v>43</v>
       </c>
@@ -1056,7 +1446,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="33.75" thickBot="1">
       <c r="A6" s="4" t="s">
         <v>46</v>
       </c>
@@ -1073,7 +1463,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="33.75" thickBot="1">
       <c r="A7" s="4" t="s">
         <v>48</v>
       </c>
@@ -1090,7 +1480,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="17.25" thickBot="1">
       <c r="A8" s="4" t="s">
         <v>51</v>
       </c>
@@ -1107,7 +1497,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="33.75" thickBot="1">
       <c r="A9" s="4" t="s">
         <v>52</v>
       </c>
@@ -1124,7 +1514,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="17.25" thickBot="1">
       <c r="A10" s="4" t="s">
         <v>53</v>
       </c>
@@ -1141,7 +1531,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="17.25" thickBot="1">
       <c r="A11" s="4" t="s">
         <v>56</v>
       </c>
@@ -1158,7 +1548,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="17.25" thickBot="1">
       <c r="A12" s="4" t="s">
         <v>59</v>
       </c>
@@ -1175,7 +1565,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="33.75" thickBot="1">
       <c r="A13" s="4" t="s">
         <v>61</v>
       </c>
@@ -1192,7 +1582,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="33.75" thickBot="1">
       <c r="A14" s="4" t="s">
         <v>63</v>
       </c>
@@ -1209,7 +1599,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="33.75" thickBot="1">
       <c r="A15" s="4" t="s">
         <v>64</v>
       </c>
@@ -1226,7 +1616,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="33.75" thickBot="1">
       <c r="A16" s="4" t="s">
         <v>65</v>
       </c>
@@ -1243,7 +1633,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="83.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="33.75" thickBot="1">
       <c r="A17" s="4" t="s">
         <v>67</v>
       </c>
@@ -1260,7 +1650,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="33.75" thickBot="1">
       <c r="A18" s="4" t="s">
         <v>69</v>
       </c>
@@ -1277,7 +1667,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="17.25" thickBot="1">
       <c r="A19" s="4" t="s">
         <v>72</v>
       </c>
@@ -1294,7 +1684,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="17.25" thickBot="1">
       <c r="A20" s="4" t="s">
         <v>73</v>
       </c>
@@ -1311,7 +1701,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="33.75" thickBot="1">
       <c r="A21" s="4" t="s">
         <v>75</v>
       </c>
@@ -1328,7 +1718,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="17.25" thickBot="1">
       <c r="A22" s="4" t="s">
         <v>77</v>
       </c>
@@ -1345,7 +1735,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="17.25" thickBot="1">
       <c r="A23" s="4" t="s">
         <v>79</v>
       </c>
@@ -1362,7 +1752,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="33.75" thickBot="1">
       <c r="A24" s="4" t="s">
         <v>80</v>
       </c>
@@ -1379,7 +1769,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="17.25" thickBot="1">
       <c r="A25" s="4" t="s">
         <v>81</v>
       </c>
@@ -1396,7 +1786,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="17.25" thickBot="1">
       <c r="A26" s="4" t="s">
         <v>83</v>
       </c>
@@ -1413,7 +1803,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="17.25" thickBot="1">
       <c r="A27" s="4" t="s">
         <v>84</v>
       </c>
@@ -1430,7 +1820,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="17.25" thickBot="1">
       <c r="A28" s="4" t="s">
         <v>85</v>
       </c>
@@ -1447,7 +1837,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="66.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="17.25" thickBot="1">
       <c r="A29" s="4" t="s">
         <v>86</v>
       </c>
@@ -1464,7 +1854,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="17.25" thickBot="1">
       <c r="A30" s="4" t="s">
         <v>87</v>
       </c>
@@ -1481,8 +1871,1464 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="A32" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{069951F5-B7F9-4391-8DC2-F67ED9C3433D}">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="32.75" customWidth="1"/>
+    <col min="2" max="2" width="34.375" customWidth="1"/>
+    <col min="3" max="3" width="28.5" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
+    <col min="5" max="5" width="48.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15" customHeight="1" thickBot="1">
+      <c r="A1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A2" s="6"/>
+      <c r="B2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="17.25" thickBot="1">
+      <c r="A3" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="50.25" thickBot="1">
+      <c r="A4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="50.25" thickBot="1">
+      <c r="A7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A8" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A9" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A10" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A11" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A12" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A13" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="50.25" thickBot="1">
+      <c r="A14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A15" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="50.25" thickBot="1">
+      <c r="A17" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A18" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A20" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A21" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A22" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A23" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A24" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A25" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A26" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A27" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A28" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A29" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A30" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A31" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:E31" xr:uid="{069951F5-B7F9-4391-8DC2-F67ED9C3433D}"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8B96215-D402-4CB0-966C-303E5554B560}">
+  <dimension ref="A1:E53"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="25.25" customWidth="1"/>
+    <col min="2" max="2" width="25.375" customWidth="1"/>
+    <col min="3" max="3" width="29.875" customWidth="1"/>
+    <col min="4" max="4" width="34.375" customWidth="1"/>
+    <col min="5" max="5" width="50.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15" thickBot="1">
+      <c r="A1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="8"/>
+      <c r="D1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="33.75" thickBot="1">
+      <c r="A2" s="6"/>
+      <c r="B2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="50.25" thickBot="1">
+      <c r="A3" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="116.25" thickBot="1">
+      <c r="A4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="99.75" thickBot="1">
+      <c r="A7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="99.75" thickBot="1">
+      <c r="A8" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A9" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="99.75" thickBot="1">
+      <c r="A10" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A11" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A12" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="83.25" thickBot="1">
+      <c r="A13" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="99.75" thickBot="1">
+      <c r="A14" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A15" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="99.75" thickBot="1">
+      <c r="A17" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="83.25" thickBot="1">
+      <c r="A18" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="83.25" thickBot="1">
+      <c r="A19" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A20" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A21" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="83.25" thickBot="1">
+      <c r="A22" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A23" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A24" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A25" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="83.25" thickBot="1">
+      <c r="A26" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="83.25" thickBot="1">
+      <c r="A27" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A28" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A29" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A30" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A31" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A32" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="116.25" thickBot="1">
+      <c r="A33" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="83.25" thickBot="1">
+      <c r="A34" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="50.25" thickBot="1">
+      <c r="A35" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="83.25" thickBot="1">
+      <c r="A36" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="99.75" thickBot="1">
+      <c r="A37" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="50.25" thickBot="1">
+      <c r="A38" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="83.25" thickBot="1">
+      <c r="A39" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="83.25" thickBot="1">
+      <c r="A40" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="116.25" thickBot="1">
+      <c r="A41" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="83.25" thickBot="1">
+      <c r="A42" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A43" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="99.75" thickBot="1">
+      <c r="A44" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="99.75" thickBot="1">
+      <c r="A45" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A46" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="99.75" thickBot="1">
+      <c r="A47" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="99.75" thickBot="1">
+      <c r="A48" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="83.25" thickBot="1">
+      <c r="A49" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="66.75" thickBot="1">
+      <c r="A50" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="83.25" thickBot="1">
+      <c r="A51" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="99.75" thickBot="1">
+      <c r="A52" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15" thickBot="1">
+      <c r="A53" s="9"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="3">
